--- a/data/raw/individual/ID 001/continuous/mHLEA_excel/TUM_S001_mHLEA_excel_20250716.xlsx
+++ b/data/raw/individual/ID 001/continuous/mHLEA_excel/TUM_S001_mHLEA_excel_20250716.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sarina/LRZ Sync+Share/Light Logger Study Data/raw/individual/ID 001/continuous/mHLEA_excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/MeLiDos/WP2.2.5_Data_Analysis/HildenEtAl_Dataset_2025/data/raw/individual/ID 001/continuous/mHLEA_excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{080B86E1-3190-0F4E-BE7D-6CC368A99FB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D1B64EB-9FEA-984E-8B76-27E369738570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="500" windowWidth="19180" windowHeight="10780" xr2:uid="{B80439AF-1263-4DF6-B1CE-F20A60096DC5}"/>
+    <workbookView xWindow="1160" yWindow="780" windowWidth="31980" windowHeight="17380" xr2:uid="{B80439AF-1263-4DF6-B1CE-F20A60096DC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="12">
   <si>
     <t>timestamp</t>
   </si>
@@ -68,13 +68,10 @@
     <t>I</t>
   </si>
   <si>
-    <t>8: Sport indoors</t>
+    <t>Sport indoors</t>
   </si>
   <si>
-    <t>8 Sport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 Sport </t>
+    <t>Sport</t>
   </si>
 </sst>
 </file>
@@ -1394,7 +1391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <f t="shared" si="1"/>
         <v>45428.291666666475</v>
@@ -1406,7 +1403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <f t="shared" si="1"/>
         <v>45428.333333333139</v>
@@ -1418,7 +1415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <f t="shared" si="1"/>
         <v>45428.374999999804</v>
@@ -1430,7 +1427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <f t="shared" si="1"/>
         <v>45428.416666666468</v>
@@ -1442,7 +1439,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <f t="shared" si="1"/>
         <v>45428.458333333132</v>
@@ -1454,7 +1451,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <f t="shared" si="1"/>
         <v>45428.499999999796</v>
@@ -1466,7 +1463,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <f t="shared" si="1"/>
         <v>45428.541666666461</v>
@@ -1478,7 +1475,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <f t="shared" si="1"/>
         <v>45428.583333333125</v>
@@ -1490,7 +1487,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <f t="shared" si="1"/>
         <v>45428.624999999789</v>
@@ -1498,11 +1495,14 @@
       <c r="B89" t="s">
         <v>6</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C89">
+        <v>8</v>
+      </c>
+      <c r="D89" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <f t="shared" si="1"/>
         <v>45428.666666666453</v>
@@ -1514,7 +1514,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <f t="shared" si="1"/>
         <v>45428.708333333117</v>
@@ -1526,7 +1526,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <f t="shared" si="1"/>
         <v>45428.749999999782</v>
@@ -1538,7 +1538,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <f t="shared" si="1"/>
         <v>45428.791666666446</v>
@@ -1550,7 +1550,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <f t="shared" si="1"/>
         <v>45428.83333333311</v>
@@ -1562,7 +1562,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <f t="shared" si="1"/>
         <v>45428.874999999774</v>
@@ -1574,7 +1574,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <f t="shared" si="1"/>
         <v>45428.916666666439</v>
@@ -1778,7 +1778,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <f t="shared" si="1"/>
         <v>45429.624999999731</v>
@@ -1790,7 +1790,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <f t="shared" si="1"/>
         <v>45429.666666666395</v>
@@ -1798,11 +1798,14 @@
       <c r="B114" t="s">
         <v>5</v>
       </c>
-      <c r="C114" t="s">
+      <c r="C114">
+        <v>8</v>
+      </c>
+      <c r="D114" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <f t="shared" si="1"/>
         <v>45429.708333333059</v>
@@ -1810,11 +1813,14 @@
       <c r="B115" t="s">
         <v>5</v>
       </c>
-      <c r="C115" t="s">
+      <c r="C115">
+        <v>8</v>
+      </c>
+      <c r="D115" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <f t="shared" si="1"/>
         <v>45429.749999999724</v>
@@ -1826,7 +1832,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <f t="shared" si="1"/>
         <v>45429.791666666388</v>
@@ -1834,11 +1840,14 @@
       <c r="B117" t="s">
         <v>7</v>
       </c>
-      <c r="C117" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C117">
+        <v>8</v>
+      </c>
+      <c r="D117" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <f t="shared" si="1"/>
         <v>45429.833333333052</v>
@@ -1850,7 +1859,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <f t="shared" si="1"/>
         <v>45429.874999999716</v>
@@ -1862,7 +1871,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <f t="shared" si="1"/>
         <v>45429.91666666638</v>
@@ -1874,7 +1883,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <f t="shared" si="1"/>
         <v>45429.958333333045</v>
@@ -1886,7 +1895,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <f t="shared" si="1"/>
         <v>45429.999999999709</v>
@@ -1898,7 +1907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <f t="shared" si="1"/>
         <v>45430.041666666373</v>
@@ -1910,7 +1919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <f t="shared" si="1"/>
         <v>45430.083333333037</v>
@@ -1922,7 +1931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <f t="shared" si="1"/>
         <v>45430.124999999702</v>
@@ -1934,7 +1943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <f t="shared" si="1"/>
         <v>45430.166666666366</v>
@@ -1946,7 +1955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <f t="shared" si="1"/>
         <v>45430.20833333303</v>
@@ -1958,7 +1967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <f t="shared" si="1"/>
         <v>45430.249999999694</v>
